--- a/docs/moodle-load-and-storage-results.xlsx
+++ b/docs/moodle-load-and-storage-results.xlsx
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>admin / see MOODLE_ADMIN_PASSWORD in .env</t>
+          <t>admin / password in .env (MOODLE_ADMIN_PASSWORD)</t>
         </is>
       </c>
       <c r="C18" s="22" t="n"/>
